--- a/IDSL.IPA/inst/extdata/IPA_parameters.xlsx
+++ b/IDSL.IPA/inst/extdata/IPA_parameters.xlsx
@@ -1,31 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\ABCD_project_SFB\IDSL.IPA\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\node2\IDSL.Github\IDSL.IPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43D1370-6A3B-46E6-B5A7-F01C71811C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23145" windowHeight="9285"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="1" r:id="rId1"/>
     <sheet name="IPA_targeted" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="189">
   <si>
     <t>0-100</t>
   </si>
@@ -117,9 +129,6 @@
     <t>Chromatographic peak detection</t>
   </si>
   <si>
-    <t>"RetentionIndex" or "Polynomial"</t>
-  </si>
-  <si>
     <t>PARAM0024</t>
   </si>
   <si>
@@ -213,9 +222,6 @@
     <t>Perform recursive mass correction</t>
   </si>
   <si>
-    <t>RetentionIndex</t>
-  </si>
-  <si>
     <t>Global parameters (required)</t>
   </si>
   <si>
@@ -247,12 +253,6 @@
   </si>
   <si>
     <t>"YES" OR "NO" (When "YES", fill out PARAM0030-PARAM0034)</t>
-  </si>
-  <si>
-    <t>1-10 (integer) (Fill out when PARAM0032 is "RetentionIndex")</t>
-  </si>
-  <si>
-    <t>1-10 (integer) (Fill out when PARAM0032 is "Polynomial")</t>
   </si>
   <si>
     <t>Data import and export (required)</t>
@@ -481,14 +481,68 @@
     <t>Select "Sample Mode" or "Peak Mode"</t>
   </si>
   <si>
-    <t>See Figure S.13 in the Supporting Information of the manuscript</t>
-  </si>
-  <si>
     <t>Perform RT correction using recurring endogenous markers as reference peaks</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Retention time correction method. The </t>
+    <t>Reference file location address</t>
+  </si>
+  <si>
+    <t>Input data location address (MS1 level HRMS data)</t>
+  </si>
+  <si>
+    <t>Output location address (MS1 processed data)</t>
+  </si>
+  <si>
+    <t>Mass difference between ion-pairs. This module always pairs dominant ions with lower intensity ions in a fixed distance. To pair dominant ions with lower mass ions, negative values should be used for this parameter.</t>
+  </si>
+  <si>
+    <t>"All" OR a list of semicolon separated of selected samples including their extensions with no extra space (case sensitive)</t>
+  </si>
+  <si>
+    <t>≥ 1 (integer) Greater numbers are beneficial to generate more reproducible baselines.</t>
+  </si>
+  <si>
+    <t>Minimum Intensity height for chromatographic peaks</t>
+  </si>
+  <si>
+    <t>Peak annotation on individual untargeted peaklists using a reference database of m/z and RT</t>
+  </si>
+  <si>
+    <t>Generate aligned peak tables and correlation lists for the aligned peak height table</t>
+  </si>
+  <si>
+    <t>Mass accuracy (Da) to cluster m/z values and generate extracted ion chromatograms (EICs)</t>
+  </si>
+  <si>
+    <t>Minimum S/N for chromatographic peaks calculated by the baseline S/N method</t>
+  </si>
+  <si>
+    <t>≤ 0.01</t>
+  </si>
+  <si>
+    <t>Mass accuracy (Da) to cluster integrated m/z values across multiple samples</t>
+  </si>
+  <si>
+    <t>Mass accuracy (Da)</t>
+  </si>
+  <si>
+    <t>https://github.com/idslme/IDSL.IPA/wiki/IPA_targeted</t>
+  </si>
+  <si>
+    <t>Generate untargeted peaklists for individual HRMS files</t>
+  </si>
+  <si>
+    <t>PARAM_ALG1</t>
+  </si>
+  <si>
+    <t>PARAM_ALG2</t>
+  </si>
+  <si>
+    <t>0.5-1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Maximum redundant aligned peak flagging threshold (%) within three times of the retention time window shown in </t>
     </r>
     <r>
       <rPr>
@@ -498,7 +552,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>RetentionIndex</t>
+      <t>PARAM0036</t>
     </r>
     <r>
       <rPr>
@@ -507,7 +561,62 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> method has better performance relative to the </t>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Minimum threshold for the correlation method</t>
+  </si>
+  <si>
+    <t>Statistical method to calculate pairwise correlations to group potential recurring adducts, in-source products and fragment peaks in separate lists. Pearson and Spearman tests should be used for linear and monotonic correlations, respectively.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">It must be in </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>*.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> format with the file extension. Three column headers with 'm/z', 'RT', 'name' must be available in the spreadsheet</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>"YES" OR "NO"(When "YES", fill out the `</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>IPA_targeted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>` tab)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Perform targeted analysis (Applicable only for the '</t>
     </r>
     <r>
       <rPr>
@@ -517,7 +626,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Polynomial</t>
+      <t>IPA_targeted</t>
     </r>
     <r>
       <rPr>
@@ -526,7 +635,66 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> method; but the </t>
+      <t>' module)</t>
+    </r>
+  </si>
+  <si>
+    <t>See Figure 3 in the main manuscript</t>
+  </si>
+  <si>
+    <t>Pearson</t>
+  </si>
+  <si>
+    <t>(Default = "Pearson"), or "Spearman"</t>
+  </si>
+  <si>
+    <t>PARAM_ALG3</t>
+  </si>
+  <si>
+    <t>11-1000 (integer) (Select `0` to skip calculating ancillary chromatography parameters for faster computations)</t>
+  </si>
+  <si>
+    <t>Minimum number of complete observation for an aligned peak</t>
+  </si>
+  <si>
+    <t>[3 - Number of samples] Select this variable depending on the number of samples</t>
+  </si>
+  <si>
+    <t>PARAM_ALG4</t>
+  </si>
+  <si>
+    <t>"YES" OR "NO"(When "YES", fill out PARAM0029-PARAM_ALG4)</t>
+  </si>
+  <si>
+    <t>"YES" or "NO" (When "YES", PARAM0029 must be "YES", and fill out PARAM0030-PARAM0036)</t>
+  </si>
+  <si>
+    <t>A column with a header of `Flag` is presented on the aligned peak table based on this parameter</t>
+  </si>
+  <si>
+    <t>Reference samples to detect recurring reference peaks for retention time correction.</t>
+  </si>
+  <si>
+    <t>Maximum absolute retention time deviation to merge redundant peaks (min)</t>
+  </si>
+  <si>
+    <t>a vector of comma separated m/z values</t>
+  </si>
+  <si>
+    <t>a vector of comma separated retention time values</t>
+  </si>
+  <si>
+    <t>Retention time correction, peak properties alignment and aligned peaks height table pairwise correlations</t>
+  </si>
+  <si>
+    <t>Minimum frequency (%) of the recurring reference peaks in the reference samples</t>
+  </si>
+  <si>
+    <t>Maximum ratio (%) of 13C for the integrated spectra across the chromatographic peak (Average R13C)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Minimum ratio (%) of the </t>
     </r>
     <r>
       <rPr>
@@ -536,7 +704,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>RetentionIndex</t>
+      <t>nIsoPair</t>
     </r>
     <r>
       <rPr>
@@ -545,69 +713,111 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> method may require more recurring endogenous markers for better performance.</t>
-    </r>
-  </si>
-  <si>
-    <t>Reference file location address</t>
-  </si>
-  <si>
-    <t>Input data location address (MS1 level HRMS data)</t>
-  </si>
-  <si>
-    <t>Output location address (MS1 processed data)</t>
-  </si>
-  <si>
-    <t>Mass difference between ion-pairs. This module always pairs dominant ions with lower intensity ions in a fixed distance. To pair dominant ions with lower mass ions, negative values should be used for this parameter.</t>
-  </si>
-  <si>
-    <t>"All" OR a list of semicolon separated of selected samples including their extensions with no extra space (case sensitive)</t>
-  </si>
-  <si>
-    <t>≥ 1 (integer) Greater numbers are beneficial to generate more reproducible baselines.</t>
-  </si>
-  <si>
-    <t>Minimum Intensity height for chromatographic peaks</t>
-  </si>
-  <si>
-    <t>Peak annotation on individual untargeted peaklists using a reference database of m/z and RT</t>
-  </si>
-  <si>
-    <t>Generate aligned peak tables and correlation lists for the aligned peak height table</t>
-  </si>
-  <si>
-    <t>Mass accuracy (Da) to cluster m/z values and generate extracted ion chromatograms (EICs)</t>
-  </si>
-  <si>
-    <t>Minimum S/N for chromatographic peaks calculated by the baseline S/N method</t>
-  </si>
-  <si>
-    <t>≤ 0.01</t>
-  </si>
-  <si>
-    <t>Mass accuracy (Da) to cluster integrated m/z values across multiple samples</t>
-  </si>
-  <si>
-    <t>Mass accuracy (Da)</t>
-  </si>
-  <si>
-    <t>https://github.com/idslme/IDSL.IPA/wiki/IPA_targeted</t>
-  </si>
-  <si>
-    <t>Generate untargeted peaklists for individual HRMS files</t>
-  </si>
-  <si>
-    <t>PARAM_ALG1</t>
-  </si>
-  <si>
-    <t>PARAM_ALG2</t>
-  </si>
-  <si>
-    <t>0.5-1</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Maximum redundant aligned peak flagging threshold (%) within three times of the retention time window shown in </t>
+      <t xml:space="preserve"> per number of available scans above 80% of peak height (RCS)</t>
+    </r>
+  </si>
+  <si>
+    <t>Maximum percentage (%) of missing scans (gaps) on the top 80% of raw chromatographic peaks</t>
+  </si>
+  <si>
+    <t>Use corrected retention times to minimize RT fluctuations for the peak annotation workflow. Reference retention times should be consistent with retention times in the RT correction method.</t>
+  </si>
+  <si>
+    <t>Parallelization mode to generate individual peaklists</t>
+  </si>
+  <si>
+    <t>Parallelization Mode</t>
+  </si>
+  <si>
+    <t>Minimum noise intensity threshold for the dominant ion in individual chromatogram scans</t>
+  </si>
+  <si>
+    <t>https://github.com/idslme/IDSL.IPA/wiki/Parallelization-Mode</t>
+  </si>
+  <si>
+    <r>
+      <t>List of HRMS files (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.mzXML</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.mzML</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.CDF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>"YES" OR "NO"(When "YES", fill out PARAM0007-PARAM0028)</t>
+  </si>
+  <si>
+    <t>https://github.com/idslme/IDSL.IPA/wiki/Definition-Signal-to-Noise-Ratio#2-hypothetical-baseline</t>
+  </si>
+  <si>
+    <t>Retention time tolerance (min) to detect common peaks</t>
+  </si>
+  <si>
+    <t>Save untargeted extracted ion chromatogram (EIC) figures for all peaks in the individual HRMS files</t>
+  </si>
+  <si>
+    <t>Minimum mutual percentage (%) of observation between two aligned peaks</t>
+  </si>
+  <si>
+    <t>MS1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Select the data source (MS1 or MS2) used to correct retention times.
+</t>
     </r>
     <r>
       <rPr>
@@ -617,7 +827,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>PARAM0036</t>
+      <t>Note:</t>
     </r>
     <r>
       <rPr>
@@ -626,72 +836,112 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Minimum threshold for the correlation method</t>
-  </si>
-  <si>
-    <t>Statistical method to calculate pairwise correlations to group potential recurring adducts, in-source products and fragment peaks in separate lists. Pearson and Spearman tests should be used for linear and monotonic correlations, respectively.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">It must be in </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>*.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> format with the file extension. Three column headers with 'm/z', 'RT', 'name' must be available in the spreadsheet</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>"YES" OR "NO"(When "YES", fill out the `</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>IPA_targeted</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>` tab)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Perform targeted analysis (Applicable only for the '</t>
+      <t xml:space="preserve"> This replaces the older correction method used prior to version 3.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MS1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>" or "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MS2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>". (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Note</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Select "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MS2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">" only if you are performing a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DDA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> analysis).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>IPA_targeted</t>
+      <t>MS1</t>
     </r>
     <r>
       <rPr>
@@ -700,239 +950,131 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>' module)</t>
-    </r>
-  </si>
-  <si>
-    <t>See Figure 3 in the main manuscript</t>
-  </si>
-  <si>
-    <t>Pearson</t>
-  </si>
-  <si>
-    <t>(Default = "Pearson"), or "Spearman"</t>
-  </si>
-  <si>
-    <t>PARAM_ALG3</t>
-  </si>
-  <si>
-    <t>11-1000 (integer) (Select `0` to skip calculating ancillary chromatography parameters for faster computations)</t>
-  </si>
-  <si>
-    <t>Minimum number of complete observation for an aligned peak</t>
-  </si>
-  <si>
-    <t>[3 - Number of samples] Select this variable depending on the number of samples</t>
-  </si>
-  <si>
-    <t>PARAM_ALG4</t>
-  </si>
-  <si>
-    <t>"YES" OR "NO"(When "YES", fill out PARAM0029-PARAM_ALG4)</t>
-  </si>
-  <si>
-    <t>"YES" or "NO" (When "YES", PARAM0029 must be "YES", and fill out PARAM0030-PARAM0036)</t>
-  </si>
-  <si>
-    <t>A column with a header of `Flag` is presented on the aligned peak table based on this parameter</t>
-  </si>
-  <si>
-    <t>Reference samples to detect recurring reference peaks for retention time correction.</t>
-  </si>
-  <si>
-    <t>Maximum absolute retention time deviation to merge redundant peaks (min)</t>
-  </si>
-  <si>
-    <t>a vector of comma separated m/z values</t>
-  </si>
-  <si>
-    <t>a vector of comma separated retention time values</t>
-  </si>
-  <si>
-    <t>Retention time correction, peak properties alignment and aligned peaks height table pairwise correlations</t>
-  </si>
-  <si>
-    <t>Minimum percentage (%) of complete observation for an aligned peak</t>
-  </si>
-  <si>
-    <t>Minimum frequency (%) of the recurring reference peaks in the reference samples</t>
-  </si>
-  <si>
-    <t>Maximum ratio (%) of 13C for the integrated spectra across the chromatographic peak (Average R13C)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Minimum ratio (%) of the </t>
+      <t xml:space="preserve"> data, enter the number of reference ion markers to use for the Retention Index correction method.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1-10 (integer) (Only required if </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PARAM0032</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> is set to "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MS1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>").</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>nIsoPair</t>
-    </r>
-    <r>
-      <rPr>
+      <t>DDA</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> per number of available scans above 80% of peak height (RCS)</t>
-    </r>
-  </si>
-  <si>
-    <t>Maximum percentage (%) of missing scans (gaps) on the top 80% of raw chromatographic peaks</t>
-  </si>
-  <si>
-    <t>Use corrected retention times to minimize RT fluctuations for the peak annotation workflow. Reference retention times should be consistent with retention times in the RT correction method.</t>
-  </si>
-  <si>
-    <t>Parallelization mode to generate individual peaklists</t>
-  </si>
-  <si>
-    <t>Parallelization Mode</t>
-  </si>
-  <si>
-    <t>Minimum noise intensity threshold for the dominant ion in individual chromatogram scans</t>
-  </si>
-  <si>
-    <t>https://github.com/idslme/IDSL.IPA/wiki/Parallelization-Mode</t>
-  </si>
-  <si>
-    <r>
-      <t>List of HRMS files (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
+      <t xml:space="preserve"> MS2</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>.mzXML</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.mzML</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.CDF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Number of endogenous reference m/z peaks for </t>
+      <t xml:space="preserve"> data, enter the polynomial degree to use for the polynomial regression correction method.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1-10 (integer) (Only required if </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>RetentionIndex</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to correct retention times using endogenous reference markers</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Polynomial degree for </t>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PARAM0032</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> is set to "</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Polynomial</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> regression</t>
-    </r>
-  </si>
-  <si>
-    <t>"YES" OR "NO"(When "YES", fill out PARAM0007-PARAM0028)</t>
-  </si>
-  <si>
-    <t>https://github.com/idslme/IDSL.IPA/wiki/Definition-Signal-to-Noise-Ratio#2-hypothetical-baseline</t>
-  </si>
-  <si>
-    <t>Retention time tolerance (min) to detect common peaks</t>
-  </si>
-  <si>
-    <t>Save untargeted extracted ion chromatogram (EIC) figures for all peaks in the individual HRMS files</t>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MS2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>").</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000000000"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1045,6 +1187,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1441,7 +1591,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1524,9 +1674,6 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1548,28 +1695,28 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1839,7 +1986,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1890,17 +2037,11 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2386,391 +2527,391 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F53"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.85546875" style="38" customWidth="1"/>
-    <col min="2" max="2" width="19" style="39" customWidth="1"/>
-    <col min="3" max="3" width="66" style="40" customWidth="1"/>
-    <col min="4" max="4" width="72" style="42" customWidth="1"/>
-    <col min="5" max="5" width="68.85546875" style="43" customWidth="1"/>
-    <col min="6" max="6" width="51.42578125" style="42" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="37"/>
+    <col min="1" max="1" width="42.81640625" style="37" customWidth="1"/>
+    <col min="2" max="2" width="19" style="38" customWidth="1"/>
+    <col min="3" max="3" width="66" style="39" customWidth="1"/>
+    <col min="4" max="4" width="72" style="41" customWidth="1"/>
+    <col min="5" max="5" width="68.81640625" style="42" customWidth="1"/>
+    <col min="6" max="6" width="51.453125" style="41" customWidth="1"/>
+    <col min="7" max="16384" width="9.1796875" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="36" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:6" s="35" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="35" t="s">
+      <c r="B1" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="131" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="133" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="190" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" s="32" t="s">
+      <c r="E1" s="130" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="132" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="187" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="80" t="s">
-        <v>147</v>
-      </c>
-      <c r="D2" s="81" t="s">
+      <c r="C2" s="79" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="82" t="s">
-        <v>186</v>
-      </c>
-      <c r="F2" s="172"/>
-    </row>
-    <row r="3" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="191"/>
+      <c r="E2" s="81" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2" s="169"/>
+    </row>
+    <row r="3" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="188"/>
       <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="F3" s="173"/>
-    </row>
-    <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="191"/>
+      <c r="E3" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" s="170"/>
+    </row>
+    <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="188"/>
       <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="173"/>
-    </row>
-    <row r="5" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="191"/>
+      <c r="E4" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="170"/>
+    </row>
+    <row r="5" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="188"/>
       <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F5" s="173"/>
-    </row>
-    <row r="6" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="191"/>
+        <v>27</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="170"/>
+    </row>
+    <row r="6" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="188"/>
       <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="F6" s="161" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="192"/>
-      <c r="B7" s="86" t="s">
+      <c r="E6" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="F6" s="158" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="189"/>
+      <c r="B7" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="87" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="88">
+      <c r="C7" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="87">
         <v>1</v>
       </c>
-      <c r="E7" s="89" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="186" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="23.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="211" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="45" t="s">
+      <c r="E7" s="88" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="183" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="23.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="208" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="134"/>
-    </row>
-    <row r="9" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="212"/>
+      <c r="C8" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E8" s="47"/>
+      <c r="F8" s="133"/>
+    </row>
+    <row r="9" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="209"/>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="F9" s="135"/>
-    </row>
-    <row r="10" spans="1:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="212"/>
-      <c r="B10" s="162" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="134"/>
+    </row>
+    <row r="10" spans="1:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="209"/>
+      <c r="B10" s="159" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="163" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" s="164" t="s">
+      <c r="C10" s="160" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="161" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="165" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" s="166"/>
-    </row>
-    <row r="11" spans="1:6" ht="34.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="213"/>
-      <c r="B11" s="53" t="s">
+      <c r="E10" s="162" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="163"/>
+    </row>
+    <row r="11" spans="1:6" ht="34.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="210"/>
+      <c r="B11" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="54" t="s">
-        <v>134</v>
-      </c>
-      <c r="D11" s="55" t="str">
+      <c r="C11" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="54" t="str">
         <f>CONCATENATE(D8, "/IDSL.IPA")</f>
         <v>/path/to/folder/MS1/IDSL.IPA</v>
       </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="180"/>
-    </row>
-    <row r="12" spans="1:6" ht="36.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="185" t="s">
-        <v>180</v>
-      </c>
-      <c r="B12" s="182" t="s">
-        <v>127</v>
-      </c>
-      <c r="C12" s="183" t="s">
-        <v>179</v>
-      </c>
-      <c r="D12" s="182" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" s="184" t="s">
-        <v>128</v>
-      </c>
-      <c r="F12" s="187" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="214" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13" s="83" t="s">
+      <c r="E11" s="55"/>
+      <c r="F11" s="177"/>
+    </row>
+    <row r="12" spans="1:6" ht="36.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="182" t="s">
+        <v>173</v>
+      </c>
+      <c r="B12" s="179" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="180" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12" s="179" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="181" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="184" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="211" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="57" t="s">
-        <v>181</v>
-      </c>
-      <c r="D13" s="84">
+      <c r="C13" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="83">
         <v>500</v>
       </c>
-      <c r="E13" s="85" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="209" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="69" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="215"/>
-      <c r="B14" s="90" t="s">
+      <c r="E13" s="84" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="206" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="212"/>
+      <c r="B14" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="91" t="s">
+      <c r="C14" s="90" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="91">
+        <v>1.003354835336</v>
+      </c>
+      <c r="E14" s="92" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="207"/>
+    </row>
+    <row r="15" spans="1:6" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="198" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="62" t="s">
         <v>135</v>
       </c>
-      <c r="D14" s="92">
-        <v>1.003354835336</v>
-      </c>
-      <c r="E14" s="93" t="s">
-        <v>108</v>
-      </c>
-      <c r="F14" s="210"/>
-    </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="201" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="63" t="s">
-        <v>141</v>
-      </c>
-      <c r="D15" s="64">
+      <c r="D15" s="63">
         <v>0.01</v>
       </c>
-      <c r="E15" s="65" t="s">
-        <v>143</v>
-      </c>
-      <c r="F15" s="136"/>
-    </row>
-    <row r="16" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202"/>
+      <c r="E15" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="F15" s="135"/>
+    </row>
+    <row r="16" spans="1:6" ht="33.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="199"/>
       <c r="B16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D16" s="8">
         <v>0.05</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="137"/>
-    </row>
-    <row r="17" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="202"/>
+        <v>44</v>
+      </c>
+      <c r="F16" s="136"/>
+    </row>
+    <row r="17" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="199"/>
       <c r="B17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D17" s="8">
         <v>12</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="157" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="34.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="202"/>
-      <c r="B18" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="154" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="34.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="199"/>
+      <c r="B18" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="74" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="75">
+      <c r="C18" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="74">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="E18" s="76" t="s">
+      <c r="E18" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="168" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="200" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="171" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="203" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="71" t="s">
+      <c r="D19" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="72" t="s">
+      <c r="E19" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="181" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="204"/>
+      <c r="F19" s="178" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="201"/>
       <c r="B20" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D20" s="12">
         <v>100</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="F20" s="154" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="204"/>
+        <v>131</v>
+      </c>
+      <c r="F20" s="151" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="201"/>
       <c r="B21" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D21" s="13">
         <v>1000</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="F21" s="138"/>
-    </row>
-    <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="204"/>
+        <v>44</v>
+      </c>
+      <c r="F21" s="137"/>
+    </row>
+    <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="201"/>
       <c r="B22" s="10" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D22" s="12">
         <v>30</v>
@@ -2778,35 +2919,35 @@
       <c r="E22" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="F22" s="154" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="204"/>
+      <c r="F22" s="151" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="36.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="201"/>
       <c r="B23" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D23" s="12">
         <v>2</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="F23" s="188" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="204"/>
+        <v>64</v>
+      </c>
+      <c r="F23" s="185" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="37.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="201"/>
       <c r="B24" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="111" t="s">
-        <v>176</v>
+        <v>30</v>
+      </c>
+      <c r="C24" s="110" t="s">
+        <v>169</v>
       </c>
       <c r="D24" s="12">
         <v>30</v>
@@ -2814,223 +2955,221 @@
       <c r="E24" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="F24" s="189"/>
-    </row>
-    <row r="25" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="204"/>
-      <c r="B25" s="120" t="s">
-        <v>32</v>
+      <c r="F24" s="186"/>
+    </row>
+    <row r="25" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="201"/>
+      <c r="B25" s="119" t="s">
+        <v>31</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="D25" s="123">
+        <v>168</v>
+      </c>
+      <c r="D25" s="122">
         <v>100</v>
       </c>
       <c r="E25" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F25" s="159" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="204"/>
-      <c r="B26" s="120" t="s">
-        <v>33</v>
+      <c r="F25" s="156" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="201"/>
+      <c r="B26" s="119" t="s">
+        <v>32</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="123">
+        <v>58</v>
+      </c>
+      <c r="D26" s="122">
         <v>1</v>
       </c>
       <c r="E26" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="155" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" s="153" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="204"/>
-      <c r="B27" s="152" t="s">
+      <c r="F26" s="152" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="39" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="201"/>
+      <c r="B27" s="150" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="122">
+        <v>2</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="152" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="202"/>
+      <c r="B28" s="120" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" s="123">
-        <v>2</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" s="155" t="s">
+      <c r="C28" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="123">
+        <v>100</v>
+      </c>
+      <c r="E28" s="78" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28" s="138" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="40.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="193" t="s">
+        <v>166</v>
+      </c>
+      <c r="B29" s="113" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="93" t="s">
+        <v>125</v>
+      </c>
+      <c r="D29" s="116" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="94" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="139"/>
+    </row>
+    <row r="30" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="194"/>
+      <c r="B30" s="114" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="D30" s="117" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" s="140"/>
+    </row>
+    <row r="31" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="194"/>
+      <c r="B31" s="114" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" s="117">
+        <v>50</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F31" s="140"/>
+    </row>
+    <row r="32" spans="1:6" ht="62" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="194"/>
+      <c r="B32" s="114" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D32" s="117" t="s">
+        <v>182</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F32" s="140"/>
+    </row>
+    <row r="33" spans="1:6" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="194"/>
+      <c r="B33" s="114" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="D33" s="117">
+        <v>5</v>
+      </c>
+      <c r="E33" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="F33" s="155" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="44" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="194"/>
+      <c r="B34" s="115" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="111" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="205"/>
-      <c r="B28" s="121" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="77" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" s="124">
-        <v>100</v>
-      </c>
-      <c r="E28" s="79" t="s">
-        <v>161</v>
-      </c>
-      <c r="F28" s="139" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="40.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="196" t="s">
-        <v>172</v>
-      </c>
-      <c r="B29" s="114" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="D29" s="117" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="95" t="s">
-        <v>73</v>
-      </c>
-      <c r="F29" s="140"/>
-    </row>
-    <row r="30" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="197"/>
-      <c r="B30" s="115" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="D30" s="118" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="F30" s="141"/>
-    </row>
-    <row r="31" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="197"/>
-      <c r="B31" s="115" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="D31" s="118">
-        <v>50</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="F31" s="141"/>
-    </row>
-    <row r="32" spans="1:6" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="197"/>
-      <c r="B32" s="115" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="D32" s="118" t="s">
-        <v>62</v>
-      </c>
-      <c r="E32" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="F32" s="141" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="197"/>
-      <c r="B33" s="115" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="D33" s="118">
-        <v>5</v>
-      </c>
-      <c r="E33" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" s="158" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="197"/>
-      <c r="B34" s="116" t="s">
+      <c r="D34" s="118">
+        <v>3</v>
+      </c>
+      <c r="E34" s="112" t="s">
+        <v>188</v>
+      </c>
+      <c r="F34" s="141"/>
+    </row>
+    <row r="35" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="195"/>
+      <c r="B35" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="D34" s="119">
-        <v>3</v>
-      </c>
-      <c r="E34" s="113" t="s">
-        <v>75</v>
-      </c>
-      <c r="F34" s="142"/>
-    </row>
-    <row r="35" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="198"/>
-      <c r="B35" s="122" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="108" t="s">
-        <v>144</v>
-      </c>
-      <c r="D35" s="110">
+      <c r="C35" s="107" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="109">
         <f>D15</f>
         <v>0.01</v>
       </c>
-      <c r="E35" s="109" t="s">
-        <v>143</v>
-      </c>
-      <c r="F35" s="143"/>
-    </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="198"/>
+      <c r="E35" s="108" t="s">
+        <v>137</v>
+      </c>
+      <c r="F35" s="142"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="195"/>
       <c r="B36" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="108" t="s">
-        <v>188</v>
-      </c>
-      <c r="D36" s="110">
+        <v>41</v>
+      </c>
+      <c r="C36" s="107" t="s">
+        <v>179</v>
+      </c>
+      <c r="D36" s="109">
         <f>D16</f>
         <v>0.05</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="F36" s="144"/>
-    </row>
-    <row r="37" spans="1:6" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="199"/>
+        <v>44</v>
+      </c>
+      <c r="F36" s="143"/>
+    </row>
+    <row r="37" spans="1:6" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="196"/>
       <c r="B37" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="175" t="s">
-        <v>151</v>
+        <v>42</v>
+      </c>
+      <c r="C37" s="172" t="s">
+        <v>145</v>
       </c>
       <c r="D37" s="22">
         <v>25</v>
@@ -3038,217 +3177,217 @@
       <c r="E37" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="F37" s="174" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="74.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="199"/>
+      <c r="F37" s="171" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="74.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="196"/>
       <c r="B38" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C38" s="175" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" s="172" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="E38" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="D38" s="22" t="s">
+      <c r="F38" s="171"/>
+    </row>
+    <row r="39" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="196"/>
+      <c r="B39" s="173" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" s="174" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="175">
+        <v>0.75</v>
+      </c>
+      <c r="E39" s="176" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39" s="171"/>
+    </row>
+    <row r="40" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="196"/>
+      <c r="B40" s="173" t="s">
+        <v>154</v>
+      </c>
+      <c r="C40" s="174" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" s="175">
+        <v>3</v>
+      </c>
+      <c r="E40" s="176" t="s">
+        <v>157</v>
+      </c>
+      <c r="F40" s="171"/>
+    </row>
+    <row r="41" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="197"/>
+      <c r="B41" s="95" t="s">
         <v>158</v>
       </c>
-      <c r="E38" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="F38" s="174"/>
-    </row>
-    <row r="39" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="199"/>
-      <c r="B39" s="176" t="s">
-        <v>149</v>
-      </c>
-      <c r="C39" s="177" t="s">
-        <v>152</v>
-      </c>
-      <c r="D39" s="178">
-        <v>0.75</v>
-      </c>
-      <c r="E39" s="179" t="s">
-        <v>150</v>
-      </c>
-      <c r="F39" s="174"/>
-    </row>
-    <row r="40" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="199"/>
-      <c r="B40" s="176" t="s">
-        <v>160</v>
-      </c>
-      <c r="C40" s="177" t="s">
-        <v>162</v>
-      </c>
-      <c r="D40" s="178">
-        <v>3</v>
-      </c>
-      <c r="E40" s="179" t="s">
-        <v>163</v>
-      </c>
-      <c r="F40" s="174"/>
-    </row>
-    <row r="41" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="200"/>
-      <c r="B41" s="96" t="s">
-        <v>164</v>
-      </c>
-      <c r="C41" s="97" t="s">
-        <v>173</v>
-      </c>
-      <c r="D41" s="98">
+      <c r="C41" s="96" t="s">
+        <v>181</v>
+      </c>
+      <c r="D41" s="97">
         <v>10</v>
       </c>
-      <c r="E41" s="99" t="s">
+      <c r="E41" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="F41" s="145"/>
-    </row>
-    <row r="42" spans="1:6" ht="34.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="206" t="s">
-        <v>104</v>
-      </c>
-      <c r="B42" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="D42" s="51">
+      <c r="F41" s="144"/>
+    </row>
+    <row r="42" spans="1:6" ht="34.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="203" t="s">
+        <v>100</v>
+      </c>
+      <c r="B42" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="D42" s="50">
         <f>D35</f>
         <v>0.01</v>
       </c>
-      <c r="E42" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="F42" s="146"/>
-    </row>
-    <row r="43" spans="1:6" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="207"/>
+      <c r="E42" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="F42" s="145"/>
+    </row>
+    <row r="43" spans="1:6" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="204"/>
       <c r="B43" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D43" s="26">
         <f>2*D36</f>
         <v>0.1</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="F43" s="147"/>
-    </row>
-    <row r="44" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="208"/>
-      <c r="B44" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="146"/>
+    </row>
+    <row r="44" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="205"/>
+      <c r="B44" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" s="59">
+        <v>20</v>
+      </c>
+      <c r="E44" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" s="157" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="20.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="190" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45" s="99" t="s">
         <v>52</v>
       </c>
-      <c r="C44" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="D44" s="60">
-        <v>20</v>
-      </c>
-      <c r="E44" s="61" t="s">
-        <v>65</v>
-      </c>
-      <c r="F44" s="160" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="20.45" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="193" t="s">
+      <c r="C45" s="100" t="s">
+        <v>126</v>
+      </c>
+      <c r="D45" s="101" t="s">
+        <v>97</v>
+      </c>
+      <c r="E45" s="102"/>
+      <c r="F45" s="147"/>
+    </row>
+    <row r="46" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="191"/>
+      <c r="B46" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="F46" s="153" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="191"/>
+      <c r="B47" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="B45" s="100" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" s="101" t="s">
-        <v>132</v>
-      </c>
-      <c r="D45" s="102" t="s">
-        <v>101</v>
-      </c>
-      <c r="E45" s="103"/>
-      <c r="F45" s="148"/>
-    </row>
-    <row r="46" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="194"/>
-      <c r="B46" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="F46" s="156" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="194"/>
-      <c r="B47" s="14" t="s">
+      <c r="D47" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="F47" s="148"/>
+    </row>
+    <row r="48" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="191"/>
+      <c r="B48" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D47" s="28">
-        <v>0.01</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="F47" s="150"/>
-    </row>
-    <row r="48" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="194"/>
-      <c r="B48" s="14" t="s">
-        <v>56</v>
-      </c>
       <c r="C48" s="15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D48" s="16">
         <v>0.05</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="F48" s="149"/>
-    </row>
-    <row r="49" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A49" s="194"/>
+        <v>44</v>
+      </c>
+      <c r="F48" s="148"/>
+    </row>
+    <row r="49" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="191"/>
       <c r="B49" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D49" s="16" t="s">
         <v>26</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="F49" s="149"/>
-    </row>
-    <row r="50" spans="1:6" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="194"/>
+        <v>160</v>
+      </c>
+      <c r="F49" s="148"/>
+    </row>
+    <row r="50" spans="1:6" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="191"/>
       <c r="B50" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D50" s="16" t="s">
         <v>26</v>
@@ -3256,15 +3395,15 @@
       <c r="E50" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="F50" s="149"/>
-    </row>
-    <row r="51" spans="1:6" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="194"/>
+      <c r="F50" s="148"/>
+    </row>
+    <row r="51" spans="1:6" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="191"/>
       <c r="B51" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D51" s="16" t="s">
         <v>26</v>
@@ -3272,28 +3411,28 @@
       <c r="E51" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="F51" s="149"/>
-    </row>
-    <row r="52" spans="1:6" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="195"/>
-      <c r="B52" s="104" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" s="105" t="s">
-        <v>84</v>
-      </c>
-      <c r="D52" s="106" t="s">
+      <c r="F51" s="148"/>
+    </row>
+    <row r="52" spans="1:6" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="192"/>
+      <c r="B52" s="103" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" s="104" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="E52" s="107" t="s">
-        <v>85</v>
-      </c>
-      <c r="F52" s="151"/>
-    </row>
-    <row r="53" spans="1:6" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="D53" s="40"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="40"/>
+      <c r="E52" s="106" t="s">
+        <v>81</v>
+      </c>
+      <c r="F52" s="149"/>
+    </row>
+    <row r="53" spans="1:6" ht="16" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D53" s="39"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3309,20 +3448,20 @@
     <mergeCell ref="A13:A14"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F27" r:id="rId1" location="2-hypothetical-baseline"/>
-    <hyperlink ref="F46" r:id="rId2"/>
-    <hyperlink ref="F23" r:id="rId3"/>
-    <hyperlink ref="F22" r:id="rId4"/>
-    <hyperlink ref="F13" r:id="rId5"/>
-    <hyperlink ref="F26" r:id="rId6"/>
-    <hyperlink ref="F33" r:id="rId7"/>
-    <hyperlink ref="F18" r:id="rId8"/>
-    <hyperlink ref="F17" r:id="rId9"/>
-    <hyperlink ref="F20" r:id="rId10"/>
-    <hyperlink ref="F44" r:id="rId11"/>
-    <hyperlink ref="F6" r:id="rId12"/>
-    <hyperlink ref="F12" r:id="rId13"/>
-    <hyperlink ref="F7" r:id="rId14"/>
+    <hyperlink ref="F27" r:id="rId1" location="2-hypothetical-baseline" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F46" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F23" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F22" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F13" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F26" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="F33" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="F18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="F17" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="F20" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="F44" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="F6" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="F12" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="F7" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId15"/>
@@ -3333,88 +3472,88 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="46.42578125" style="38" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="39" customWidth="1"/>
-    <col min="3" max="3" width="60.7109375" style="40" customWidth="1"/>
-    <col min="4" max="4" width="70.85546875" style="42" customWidth="1"/>
-    <col min="5" max="5" width="63" style="43" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="37"/>
+    <col min="1" max="1" width="46.453125" style="37" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" style="38" customWidth="1"/>
+    <col min="3" max="3" width="60.7265625" style="39" customWidth="1"/>
+    <col min="4" max="4" width="70.81640625" style="41" customWidth="1"/>
+    <col min="5" max="5" width="63" style="42" customWidth="1"/>
+    <col min="6" max="16384" width="9.1796875" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="36" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:5" s="35" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="35" t="s">
+      <c r="B1" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="44" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="36" customFormat="1" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="216" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" s="32" t="s">
+      <c r="E1" s="43" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="35" customFormat="1" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="213" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="169" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="32">
+      <c r="C2" s="166" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="31">
         <f>parameters!D7</f>
         <v>1</v>
       </c>
-      <c r="E2" s="170" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="36" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="216"/>
-      <c r="B3" s="86" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" s="167" t="s">
-        <v>125</v>
-      </c>
-      <c r="D3" s="86" t="s">
-        <v>126</v>
-      </c>
-      <c r="E3" s="168" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="211" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="45" t="str">
+      <c r="E2" s="167" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="35" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="213"/>
+      <c r="B3" s="85" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="164" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="85" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="165" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="208" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="44" t="str">
         <f>parameters!B8</f>
         <v>PARAM0007</v>
       </c>
-      <c r="C4" s="46" t="str">
+      <c r="C4" s="45" t="str">
         <f>parameters!C8</f>
         <v>Input data location address (MS1 level HRMS data)</v>
       </c>
-      <c r="D4" s="47" t="str">
+      <c r="D4" s="46" t="str">
         <f>parameters!D8</f>
         <v>/path/to/folder/MS1</v>
       </c>
-      <c r="E4" s="48"/>
-    </row>
-    <row r="5" spans="1:5" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="212"/>
+      <c r="E4" s="47"/>
+    </row>
+    <row r="5" spans="1:5" ht="46.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="209"/>
       <c r="B5" s="1" t="str">
         <f>parameters!B9</f>
         <v>PARAM0008</v>
@@ -3428,11 +3567,11 @@
         <v>All</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="212"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="209"/>
       <c r="B6" s="1" t="str">
         <f>parameters!B10</f>
         <v>PARAM0009</v>
@@ -3446,119 +3585,119 @@
         <v>NO</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="36.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="209"/>
       <c r="B7" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="213"/>
-      <c r="B8" s="53" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="210"/>
+      <c r="B8" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="54" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" s="55" t="str">
-        <f>CONCATENATE(D4, "/IDSL.IPA")</f>
+      <c r="C8" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="54" t="str">
+        <f>parameters!D11</f>
         <v>/path/to/folder/MS1/IDSL.IPA</v>
       </c>
-      <c r="E8" s="56"/>
-    </row>
-    <row r="9" spans="1:5" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="218" t="s">
+      <c r="E8" s="55"/>
+    </row>
+    <row r="9" spans="1:5" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="215" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="204"/>
+      <c r="B10" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="49" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="50" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" s="52" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="207"/>
-      <c r="B10" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>93</v>
-      </c>
       <c r="D10" s="26" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="69.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="132" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="66" t="str">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="69.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="131" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="65" t="str">
         <f>parameters!B14</f>
         <v>PARAM0012</v>
       </c>
-      <c r="C11" s="129" t="str">
+      <c r="C11" s="128" t="str">
         <f>parameters!C14</f>
         <v>Mass difference between ion-pairs. This module always pairs dominant ions with lower intensity ions in a fixed distance. To pair dominant ions with lower mass ions, negative values should be used for this parameter.</v>
       </c>
-      <c r="D11" s="68">
+      <c r="D11" s="67">
         <f>parameters!D14</f>
         <v>1.003354835336</v>
       </c>
-      <c r="E11" s="67" t="str">
+      <c r="E11" s="66" t="str">
         <f>parameters!E14</f>
         <v>(Default = ∆C = 13C - 12C = 1.003354835336 to only find carbon-containing peaks), ∆S = 34S - 32S = 1.9957958356, or any numerical value</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="201" t="s">
+    <row r="12" spans="1:5" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="198" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="64" t="str">
+      <c r="B12" s="63" t="str">
         <f>parameters!B15</f>
         <v>PARAM0013</v>
       </c>
-      <c r="C12" s="125" t="str">
+      <c r="C12" s="124" t="str">
         <f>parameters!C15</f>
         <v>Mass accuracy (Da) to cluster m/z values and generate extracted ion chromatograms (EICs)</v>
       </c>
-      <c r="D12" s="64">
+      <c r="D12" s="63">
         <f>parameters!D15</f>
         <v>0.01</v>
       </c>
-      <c r="E12" s="125" t="str">
+      <c r="E12" s="124" t="str">
         <f>parameters!E15</f>
         <v>≤ 0.01</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="202"/>
+    <row r="13" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="199"/>
       <c r="B13" s="8" t="str">
         <f>parameters!B17</f>
         <v>PARAM0015</v>
       </c>
-      <c r="C13" s="126" t="str">
+      <c r="C13" s="125" t="str">
         <f>parameters!C17</f>
         <v>Smoothing window (number of MS1 scans)</v>
       </c>
@@ -3566,73 +3705,73 @@
         <f>parameters!D17</f>
         <v>12</v>
       </c>
-      <c r="E13" s="126" t="str">
+      <c r="E13" s="125" t="str">
         <f>parameters!E17</f>
         <v>≥ 5</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="219"/>
-      <c r="B14" s="75" t="str">
+    <row r="14" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="216"/>
+      <c r="B14" s="74" t="str">
         <f>parameters!B18</f>
         <v>PARAM0017</v>
       </c>
-      <c r="C14" s="127" t="str">
+      <c r="C14" s="126" t="str">
         <f>parameters!C18</f>
         <v>Peak tailing/fronting resolving power</v>
       </c>
-      <c r="D14" s="75">
+      <c r="D14" s="74">
         <f>parameters!D18</f>
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="E14" s="127" t="str">
+      <c r="E14" s="126" t="str">
         <f>parameters!E18</f>
         <v>0-0.05 (Select 0 to skip this module)</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="41.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="217" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="71" t="str">
+    <row r="15" spans="1:5" ht="41.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="214" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="70" t="str">
         <f>parameters!B20</f>
         <v>PARAM0020</v>
       </c>
-      <c r="C15" s="130" t="str">
+      <c r="C15" s="129" t="str">
         <f>parameters!C20</f>
         <v>Number of extra scans on the both sides of detected peak boundaries in the recursive analysis to reconstruct baseline</v>
       </c>
-      <c r="D15" s="71">
+      <c r="D15" s="70">
         <f>parameters!D20</f>
         <v>100</v>
       </c>
-      <c r="E15" s="72"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="205"/>
-      <c r="B16" s="78" t="str">
+      <c r="E15" s="71"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="202"/>
+      <c r="B16" s="77" t="str">
         <f>parameters!B28</f>
         <v>PARAM0028</v>
       </c>
-      <c r="C16" s="128" t="str">
+      <c r="C16" s="127" t="str">
         <f>parameters!C28</f>
         <v>Number of points to smooth individual chromatographic peaks using cubic spline method to calculate ancillary chromatography parameters</v>
       </c>
-      <c r="D16" s="78">
+      <c r="D16" s="77">
         <f>parameters!D28</f>
         <v>100</v>
       </c>
-      <c r="E16" s="128" t="str">
+      <c r="E16" s="127" t="str">
         <f>parameters!E28</f>
         <v>11-1000 (integer) (Select `0` to skip calculating ancillary chromatography parameters for faster computations)</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="42" customFormat="1" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="38"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="41"/>
+    <row r="17" spans="1:5" s="41" customFormat="1" ht="16" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="37"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/IDSL.IPA/inst/extdata/IPA_parameters.xlsx
+++ b/IDSL.IPA/inst/extdata/IPA_parameters.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\node2\IDSL.Github\IDSL.IPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43D1370-6A3B-46E6-B5A7-F01C71811C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E8856E-4A58-4B27-8E90-7BE160E54D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3015" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="parameters" sheetId="1" r:id="rId1"/>
+    <sheet name="parameters" sheetId="4" r:id="rId1"/>
     <sheet name="IPA_targeted" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="184">
   <si>
     <t>0-100</t>
   </si>
@@ -168,9 +168,6 @@
     <t>PARAM0037</t>
   </si>
   <si>
-    <t>PARAM0038</t>
-  </si>
-  <si>
     <t>≥ 0</t>
   </si>
   <si>
@@ -183,18 +180,9 @@
     <t>Reference_masses_peak_annotation.xlsx</t>
   </si>
   <si>
-    <t>PARAM0039</t>
-  </si>
-  <si>
     <t>PARAM0029</t>
   </si>
   <si>
-    <t>Retention time tolerance to detect common peaks (min)</t>
-  </si>
-  <si>
-    <t>PARAM0040</t>
-  </si>
-  <si>
     <t>PARAM0041</t>
   </si>
   <si>
@@ -228,9 +216,6 @@
     <t>Peak analysis and data reduction</t>
   </si>
   <si>
-    <t>≥ 0 (integer)</t>
-  </si>
-  <si>
     <t>≥ 1 (integer)</t>
   </si>
   <si>
@@ -249,9 +234,6 @@
     <t>PARAM0047</t>
   </si>
   <si>
-    <t>"YES" OR "NO"(When "YES", fill out PARAM0038-PARAM0040)</t>
-  </si>
-  <si>
     <t>"YES" OR "NO" (When "YES", fill out PARAM0030-PARAM0034)</t>
   </si>
   <si>
@@ -273,9 +255,6 @@
     <t>A list of semicolon separated of reference samples including their extensions (with no space after or before semicolons)</t>
   </si>
   <si>
-    <t>Number of extra scans on the both sides of peak boundaries to fill</t>
-  </si>
-  <si>
     <t>PARAM0048</t>
   </si>
   <si>
@@ -321,9 +300,6 @@
     <t>All</t>
   </si>
   <si>
-    <t>003.mzML;004.mzML</t>
-  </si>
-  <si>
     <t>c(0,0)</t>
   </si>
   <si>
@@ -337,12 +313,6 @@
   </si>
   <si>
     <t>Smoothing window (number of MS1 scans)</t>
-  </si>
-  <si>
-    <t>Gap-filling on the aligned peak tables</t>
-  </si>
-  <si>
-    <t>Perform gap-filling for the aligned peak tables</t>
   </si>
   <si>
     <r>
@@ -442,9 +412,6 @@
     <t>See Section S.2 in the Supporting Information of the manuscript</t>
   </si>
   <si>
-    <t>Graphical guide</t>
-  </si>
-  <si>
     <t>https://github.com/idslme/IDSL.IPA/wiki/Retention-Index</t>
   </si>
   <si>
@@ -464,9 +431,6 @@
   </si>
   <si>
     <t>"YES" OR "NO"(When "YES", fill out PARAM0041-PARAM0048)</t>
-  </si>
-  <si>
-    <t>/path/to/folder/MS1</t>
   </si>
   <si>
     <t>Parallelization mode</t>
@@ -812,12 +776,14 @@
     <t>Minimum mutual percentage (%) of observation between two aligned peaks</t>
   </si>
   <si>
-    <t>MS1</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Select the data source (MS1 or MS2) used to correct retention times.
-</t>
+    <t>Online Guide</t>
+  </si>
+  <si>
+    <t>Perform gap-filling using the aligned peak tables</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Retention time correction method. The </t>
     </r>
     <r>
       <rPr>
@@ -827,7 +793,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Note:</t>
+      <t>RetentionIndex</t>
     </r>
     <r>
       <rPr>
@@ -836,102 +802,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> This replaces the older correction method used prior to version 3.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>MS1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>" or "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>MS2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>". (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Note</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>: Select "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>MS2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">" only if you are performing a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DDA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> analysis).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If using </t>
+      <t xml:space="preserve"> method has better performance relative to the </t>
     </r>
     <r>
       <rPr>
@@ -941,7 +812,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>MS1</t>
+      <t>Polynomial</t>
     </r>
     <r>
       <rPr>
@@ -950,62 +821,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> data, enter the number of reference ion markers to use for the Retention Index correction method.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1-10 (integer) (Only required if </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>PARAM0032</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> is set to "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>MS1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>").</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If using </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DDA</t>
+      <t xml:space="preserve"> method; but the </t>
     </r>
     <r>
       <rPr>
@@ -1015,7 +831,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> MS2</t>
+      <t>RetentionIndex</t>
     </r>
     <r>
       <rPr>
@@ -1024,47 +840,84 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> data, enter the polynomial degree to use for the polynomial regression correction method.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1-10 (integer) (Only required if </t>
+      <t xml:space="preserve"> method may require more recurring endogenous markers for better performance.</t>
+    </r>
+  </si>
+  <si>
+    <t>ms2</t>
+  </si>
+  <si>
+    <t>"RetentionIndex" or "Polynomial"</t>
+  </si>
+  <si>
+    <t>See Figure S.13 in the Supporting Information of the manuscript</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Number of endogenous reference m/z peaks for </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>PARAM0032</t>
+      <t>RetentionIndex</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> is set to "</t>
+      <t xml:space="preserve"> to correct retention times using endogenous reference markers</t>
+    </r>
+  </si>
+  <si>
+    <t>1-10 (integer) (Fill out when PARAM0032 is "RetentionIndex")</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Polynomial degree for </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>MS2</t>
+      <t>Polynomial</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>").</t>
-    </r>
+      <t xml:space="preserve"> regression</t>
+    </r>
+  </si>
+  <si>
+    <t>1-10 (integer) (Fill out when PARAM0032 is "Polynomial")</t>
+  </si>
+  <si>
+    <t>These parameters are used later to cluster recurring peaks in the IDSL.CSA pipeline. Refer to the CSA0012 parameter in the IDSL.CSA parameter table for details.
+https://github.com/idslme/IDSL.CSA/wiki/CSA-analysis-by-IDSL.CSA#csa-msp-generation</t>
+  </si>
+  <si>
+    <t>/path/to/folder/MS1</t>
+  </si>
+  <si>
+    <t>/path/to/folder/MS1/IDSL.IPA</t>
+  </si>
+  <si>
+    <t>003.mzML;004.mzML</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +927,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000000000"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1187,14 +1040,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1591,7 +1436,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1761,18 +1606,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1830,9 +1663,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2022,15 +1852,6 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2061,9 +1882,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2145,88 +1963,88 @@
     <xf numFmtId="0" fontId="16" fillId="6" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="12" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="12" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="12" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="12" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2236,6 +2054,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2527,8 +2348,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F53"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB0673F-935A-4F0A-BDE5-F30BBFC6D834}">
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="42.81640625" style="37" customWidth="1"/>
@@ -2545,38 +2366,38 @@
         <v>28</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="130" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="132" t="s">
-        <v>112</v>
+      <c r="E1" s="125" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="127" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" s="187" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="D2" s="80" t="s">
+      <c r="C2" s="75" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="81" t="s">
-        <v>177</v>
-      </c>
-      <c r="F2" s="169"/>
+      <c r="E2" s="76" t="s">
+        <v>165</v>
+      </c>
+      <c r="F2" s="160"/>
     </row>
     <row r="3" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="188"/>
@@ -2584,15 +2405,15 @@
         <v>3</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="F3" s="170"/>
+        <v>147</v>
+      </c>
+      <c r="F3" s="161"/>
     </row>
     <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="188"/>
@@ -2600,15 +2421,13 @@
         <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>101</v>
+        <v>171</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" s="170"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="161"/>
     </row>
     <row r="5" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="188"/>
@@ -2616,15 +2435,15 @@
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F5" s="170"/>
+        <v>108</v>
+      </c>
+      <c r="F5" s="161"/>
     </row>
     <row r="6" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="188"/>
@@ -2632,286 +2451,285 @@
         <v>8</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="F6" s="158" t="s">
-        <v>140</v>
+        <v>137</v>
+      </c>
+      <c r="F6" s="149" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="189"/>
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="D7" s="87">
-        <v>1</v>
-      </c>
-      <c r="E7" s="88" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="183" t="s">
-        <v>175</v>
+      <c r="C7" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="82">
+        <v>20</v>
+      </c>
+      <c r="E7" s="83" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="174" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="23.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="208" t="s">
-        <v>72</v>
+      <c r="A8" s="190" t="s">
+        <v>66</v>
       </c>
       <c r="B8" s="44" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>120</v>
+        <v>181</v>
       </c>
       <c r="E8" s="47"/>
-      <c r="F8" s="133"/>
+      <c r="F8" s="128"/>
     </row>
     <row r="9" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="209"/>
+      <c r="A9" s="191"/>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" s="134"/>
+        <v>118</v>
+      </c>
+      <c r="F9" s="129"/>
     </row>
     <row r="10" spans="1:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="209"/>
-      <c r="B10" s="159" t="s">
+      <c r="A10" s="191"/>
+      <c r="B10" s="150" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="160" t="s">
-        <v>180</v>
-      </c>
-      <c r="D10" s="161" t="s">
+      <c r="C10" s="151" t="s">
+        <v>168</v>
+      </c>
+      <c r="D10" s="152" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="162" t="s">
-        <v>90</v>
-      </c>
-      <c r="F10" s="163"/>
+      <c r="E10" s="153" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="154"/>
     </row>
     <row r="11" spans="1:6" ht="34.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="210"/>
+      <c r="A11" s="192"/>
       <c r="B11" s="52" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="D11" s="54" t="str">
-        <f>CONCATENATE(D8, "/IDSL.IPA")</f>
-        <v>/path/to/folder/MS1/IDSL.IPA</v>
+        <v>116</v>
+      </c>
+      <c r="D11" s="54" t="s">
+        <v>182</v>
       </c>
       <c r="E11" s="55"/>
-      <c r="F11" s="177"/>
+      <c r="F11" s="168"/>
     </row>
     <row r="12" spans="1:6" ht="36.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="182" t="s">
-        <v>173</v>
-      </c>
-      <c r="B12" s="179" t="s">
+      <c r="A12" s="173" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12" s="170" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="171" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="170" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="172" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="175" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="193" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="D13" s="78">
+        <v>500</v>
+      </c>
+      <c r="E13" s="79" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="195" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="194"/>
+      <c r="B14" s="84" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="85" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" s="86">
+        <v>1.003354835336</v>
+      </c>
+      <c r="E14" s="87" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="196"/>
+    </row>
+    <row r="15" spans="1:6" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="197" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="180" t="s">
-        <v>172</v>
-      </c>
-      <c r="D12" s="179" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="181" t="s">
-        <v>124</v>
-      </c>
-      <c r="F12" s="184" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="211" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="82" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="56" t="s">
-        <v>174</v>
-      </c>
-      <c r="D13" s="83">
-        <v>500</v>
-      </c>
-      <c r="E13" s="84" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="206" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="69" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="212"/>
-      <c r="B14" s="89" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="90" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="91">
-        <v>1.003354835336</v>
-      </c>
-      <c r="E14" s="92" t="s">
-        <v>104</v>
-      </c>
-      <c r="F14" s="207"/>
-    </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="198" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="62" t="s">
-        <v>135</v>
-      </c>
-      <c r="D15" s="63">
+      <c r="D15" s="59">
         <v>0.01</v>
       </c>
-      <c r="E15" s="64" t="s">
-        <v>137</v>
-      </c>
-      <c r="F15" s="135"/>
+      <c r="E15" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="130"/>
     </row>
     <row r="16" spans="1:6" ht="33.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="199"/>
+      <c r="A16" s="198"/>
       <c r="B16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D16" s="8">
         <v>0.05</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="136"/>
+        <v>43</v>
+      </c>
+      <c r="F16" s="131"/>
     </row>
     <row r="17" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="199"/>
+      <c r="A17" s="198"/>
       <c r="B17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D17" s="8">
         <v>12</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17" s="154" t="s">
-        <v>116</v>
+        <v>75</v>
+      </c>
+      <c r="F17" s="146" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="34.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="199"/>
-      <c r="B18" s="72" t="s">
+      <c r="A18" s="198"/>
+      <c r="B18" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="73" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="74">
+      <c r="C18" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="70">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="E18" s="75" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="168" t="s">
-        <v>115</v>
+      <c r="E18" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="159" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="200" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="68" t="s">
+      <c r="A19" s="199" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="69" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="70" t="s">
+      <c r="C19" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="71" t="s">
+      <c r="E19" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="178" t="s">
-        <v>118</v>
+      <c r="F19" s="169" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="201"/>
+      <c r="A20" s="200"/>
       <c r="B20" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D20" s="12">
         <v>100</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="F20" s="151" t="s">
-        <v>117</v>
+        <v>119</v>
+      </c>
+      <c r="F20" s="143" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="201"/>
+      <c r="A21" s="200"/>
       <c r="B21" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D21" s="13">
         <v>1000</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="137"/>
+        <v>43</v>
+      </c>
+      <c r="F21" s="132"/>
     </row>
     <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="201"/>
+      <c r="A22" s="200"/>
       <c r="B22" s="10" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D22" s="12">
         <v>30</v>
@@ -2919,35 +2737,35 @@
       <c r="E22" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="F22" s="151" t="s">
-        <v>108</v>
+      <c r="F22" s="143" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="36.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="201"/>
+      <c r="A23" s="200"/>
       <c r="B23" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D23" s="12">
         <v>2</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" s="185" t="s">
-        <v>107</v>
+        <v>59</v>
+      </c>
+      <c r="F23" s="202" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="37.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="201"/>
+      <c r="A24" s="200"/>
       <c r="B24" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="110" t="s">
-        <v>169</v>
+      <c r="C24" s="105" t="s">
+        <v>157</v>
       </c>
       <c r="D24" s="12">
         <v>30</v>
@@ -2955,221 +2773,223 @@
       <c r="E24" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="F24" s="186"/>
+      <c r="F24" s="203"/>
     </row>
     <row r="25" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="201"/>
-      <c r="B25" s="119" t="s">
+      <c r="A25" s="200"/>
+      <c r="B25" s="114" t="s">
         <v>31</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="D25" s="122">
+        <v>156</v>
+      </c>
+      <c r="D25" s="117">
         <v>100</v>
       </c>
       <c r="E25" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F25" s="156" t="s">
-        <v>151</v>
+      <c r="F25" s="148" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="201"/>
-      <c r="B26" s="119" t="s">
+      <c r="A26" s="200"/>
+      <c r="B26" s="114" t="s">
         <v>32</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="122">
+        <v>54</v>
+      </c>
+      <c r="D26" s="117">
         <v>1</v>
       </c>
       <c r="E26" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="152" t="s">
-        <v>110</v>
+      <c r="F26" s="144" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="39" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="201"/>
-      <c r="B27" s="150" t="s">
+      <c r="A27" s="200"/>
+      <c r="B27" s="142" t="s">
         <v>33</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D27" s="122">
+        <v>124</v>
+      </c>
+      <c r="D27" s="117">
         <v>2</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="F27" s="152" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="144" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="201"/>
+      <c r="B28" s="115" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="72" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="118">
+        <v>100</v>
+      </c>
+      <c r="E28" s="74" t="s">
+        <v>143</v>
+      </c>
+      <c r="F28" s="133" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="40.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="176" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" s="108" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="88" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="111" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="89" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" s="134"/>
+    </row>
+    <row r="30" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="177"/>
+      <c r="B30" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D30" s="112" t="s">
+        <v>183</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="135"/>
+    </row>
+    <row r="31" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="177"/>
+      <c r="B31" s="109" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D31" s="112">
+        <v>75</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="135"/>
+    </row>
+    <row r="32" spans="1:6" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="177"/>
+      <c r="B32" s="109" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D32" s="112" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="F32" s="135" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="177"/>
+      <c r="B33" s="109" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" s="112">
+        <v>5</v>
+      </c>
+      <c r="E33" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="F33" s="147" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="177"/>
+      <c r="B34" s="110" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="106" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="202"/>
-      <c r="B28" s="120" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="76" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="123">
-        <v>100</v>
-      </c>
-      <c r="E28" s="78" t="s">
-        <v>155</v>
-      </c>
-      <c r="F28" s="138" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="40.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="193" t="s">
-        <v>166</v>
-      </c>
-      <c r="B29" s="113" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="93" t="s">
-        <v>125</v>
-      </c>
-      <c r="D29" s="116" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="94" t="s">
-        <v>71</v>
-      </c>
-      <c r="F29" s="139"/>
-    </row>
-    <row r="30" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="194"/>
-      <c r="B30" s="114" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="D30" s="117" t="s">
-        <v>94</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="F30" s="140"/>
-    </row>
-    <row r="31" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="194"/>
-      <c r="B31" s="114" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="D31" s="117">
-        <v>50</v>
-      </c>
-      <c r="E31" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="F31" s="140"/>
-    </row>
-    <row r="32" spans="1:6" ht="62" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="194"/>
-      <c r="B32" s="114" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="D32" s="117" t="s">
-        <v>182</v>
-      </c>
-      <c r="E32" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="F32" s="140"/>
-    </row>
-    <row r="33" spans="1:6" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="194"/>
-      <c r="B33" s="114" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="D33" s="117">
-        <v>5</v>
-      </c>
-      <c r="E33" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="F33" s="155" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="44" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="194"/>
-      <c r="B34" s="115" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" s="111" t="s">
-        <v>187</v>
-      </c>
-      <c r="D34" s="118">
+      <c r="D34" s="113">
         <v>3</v>
       </c>
-      <c r="E34" s="112" t="s">
-        <v>188</v>
-      </c>
-      <c r="F34" s="141"/>
+      <c r="E34" s="107" t="s">
+        <v>179</v>
+      </c>
+      <c r="F34" s="136"/>
     </row>
     <row r="35" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="195"/>
-      <c r="B35" s="121" t="s">
+      <c r="A35" s="178"/>
+      <c r="B35" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="107" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" s="109">
+      <c r="C35" s="102" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" s="104">
         <f>D15</f>
         <v>0.01</v>
       </c>
-      <c r="E35" s="108" t="s">
-        <v>137</v>
-      </c>
-      <c r="F35" s="142"/>
+      <c r="E35" s="103" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" s="137"/>
     </row>
     <row r="36" spans="1:6" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="195"/>
+      <c r="A36" s="178"/>
       <c r="B36" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="107" t="s">
-        <v>179</v>
-      </c>
-      <c r="D36" s="109">
+      <c r="C36" s="102" t="s">
+        <v>167</v>
+      </c>
+      <c r="D36" s="104">
         <f>D16</f>
         <v>0.05</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="143"/>
+        <v>43</v>
+      </c>
+      <c r="F36" s="138"/>
     </row>
     <row r="37" spans="1:6" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="196"/>
+      <c r="A37" s="179"/>
       <c r="B37" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="172" t="s">
-        <v>145</v>
+      <c r="C37" s="163" t="s">
+        <v>133</v>
       </c>
       <c r="D37" s="22">
         <v>25</v>
@@ -3177,297 +2997,240 @@
       <c r="E37" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="F37" s="171" t="s">
-        <v>161</v>
+      <c r="F37" s="162" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="74.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="196"/>
+      <c r="A38" s="179"/>
       <c r="B38" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="163" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F38" s="181" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="179"/>
+      <c r="B39" s="164" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" s="165" t="s">
+        <v>134</v>
+      </c>
+      <c r="D39" s="166">
+        <v>0.75</v>
+      </c>
+      <c r="E39" s="167" t="s">
+        <v>132</v>
+      </c>
+      <c r="F39" s="182"/>
+    </row>
+    <row r="40" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="179"/>
+      <c r="B40" s="164" t="s">
         <v>142</v>
       </c>
-      <c r="C38" s="172" t="s">
-        <v>147</v>
-      </c>
-      <c r="D38" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="F38" s="171"/>
-    </row>
-    <row r="39" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="196"/>
-      <c r="B39" s="173" t="s">
-        <v>143</v>
-      </c>
-      <c r="C39" s="174" t="s">
+      <c r="C40" s="165" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40" s="166">
+        <v>3</v>
+      </c>
+      <c r="E40" s="167" t="s">
+        <v>145</v>
+      </c>
+      <c r="F40" s="182"/>
+    </row>
+    <row r="41" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="180"/>
+      <c r="B41" s="90" t="s">
         <v>146</v>
       </c>
-      <c r="D39" s="175">
-        <v>0.75</v>
-      </c>
-      <c r="E39" s="176" t="s">
-        <v>144</v>
-      </c>
-      <c r="F39" s="171"/>
-    </row>
-    <row r="40" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="196"/>
-      <c r="B40" s="173" t="s">
-        <v>154</v>
-      </c>
-      <c r="C40" s="174" t="s">
-        <v>156</v>
-      </c>
-      <c r="D40" s="175">
-        <v>3</v>
-      </c>
-      <c r="E40" s="176" t="s">
-        <v>157</v>
-      </c>
-      <c r="F40" s="171"/>
-    </row>
-    <row r="41" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="197"/>
-      <c r="B41" s="95" t="s">
-        <v>158</v>
-      </c>
-      <c r="C41" s="96" t="s">
-        <v>181</v>
-      </c>
-      <c r="D41" s="97">
+      <c r="C41" s="91" t="s">
+        <v>169</v>
+      </c>
+      <c r="D41" s="92">
         <v>10</v>
       </c>
-      <c r="E41" s="98" t="s">
+      <c r="E41" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="F41" s="144"/>
-    </row>
-    <row r="42" spans="1:6" ht="34.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="203" t="s">
-        <v>100</v>
-      </c>
-      <c r="B42" s="48" t="s">
+      <c r="F41" s="183"/>
+    </row>
+    <row r="42" spans="1:6" ht="20.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="184" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" s="94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="95" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="96" t="s">
+        <v>89</v>
+      </c>
+      <c r="E42" s="97"/>
+      <c r="F42" s="139"/>
+    </row>
+    <row r="43" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="185"/>
+      <c r="B43" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F43" s="145" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="185"/>
+      <c r="B44" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D44" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="F44" s="140"/>
+    </row>
+    <row r="45" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="185"/>
+      <c r="B45" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D45" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="E45" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="D42" s="50">
-        <f>D35</f>
-        <v>0.01</v>
-      </c>
-      <c r="E42" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="F42" s="145"/>
-    </row>
-    <row r="43" spans="1:6" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="204"/>
-      <c r="B43" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C43" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="D43" s="26">
-        <f>2*D36</f>
-        <v>0.1</v>
-      </c>
-      <c r="E43" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F43" s="146"/>
-    </row>
-    <row r="44" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="205"/>
-      <c r="B44" s="57" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" s="58" t="s">
-        <v>78</v>
-      </c>
-      <c r="D44" s="59">
-        <v>20</v>
-      </c>
-      <c r="E44" s="60" t="s">
-        <v>63</v>
-      </c>
-      <c r="F44" s="157" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="20.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="190" t="s">
-        <v>133</v>
-      </c>
-      <c r="B45" s="99" t="s">
+      <c r="F45" s="140"/>
+    </row>
+    <row r="46" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="185"/>
+      <c r="B46" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="100" t="s">
-        <v>126</v>
-      </c>
-      <c r="D45" s="101" t="s">
-        <v>97</v>
-      </c>
-      <c r="E45" s="102"/>
-      <c r="F45" s="147"/>
-    </row>
-    <row r="46" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="191"/>
-      <c r="B46" s="14" t="s">
-        <v>53</v>
-      </c>
       <c r="C46" s="15" t="s">
-        <v>46</v>
+        <v>159</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="E46" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F46" s="153" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="191"/>
+      <c r="F46" s="140"/>
+    </row>
+    <row r="47" spans="1:6" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="185"/>
       <c r="B47" s="14" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="D47" s="16">
-        <v>0.01</v>
+        <v>76</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>26</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="F47" s="148"/>
-    </row>
-    <row r="48" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="191"/>
+        <v>25</v>
+      </c>
+      <c r="F47" s="140"/>
+    </row>
+    <row r="48" spans="1:6" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="185"/>
       <c r="B48" s="14" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D48" s="16">
-        <v>0.05</v>
+        <v>77</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>26</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="F48" s="148"/>
-    </row>
-    <row r="49" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="191"/>
-      <c r="B49" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D49" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="140"/>
+    </row>
+    <row r="49" spans="1:6" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="186"/>
+      <c r="B49" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="99" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="100" t="s">
         <v>26</v>
       </c>
-      <c r="E49" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="F49" s="148"/>
-    </row>
-    <row r="50" spans="1:6" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="191"/>
-      <c r="B50" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="148"/>
-    </row>
-    <row r="51" spans="1:6" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="191"/>
-      <c r="B51" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E51" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" s="148"/>
-    </row>
-    <row r="52" spans="1:6" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="192"/>
-      <c r="B52" s="103" t="s">
-        <v>79</v>
-      </c>
-      <c r="C52" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52" s="105" t="s">
-        <v>26</v>
-      </c>
-      <c r="E52" s="106" t="s">
-        <v>81</v>
-      </c>
-      <c r="F52" s="149"/>
-    </row>
-    <row r="53" spans="1:6" ht="16" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="D53" s="39"/>
-      <c r="E53" s="40"/>
-      <c r="F53" s="39"/>
+      <c r="E49" s="101" t="s">
+        <v>74</v>
+      </c>
+      <c r="F49" s="141"/>
+    </row>
+    <row r="50" spans="1:6" ht="16" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D50" s="39"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="A29:A41"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="A42:A49"/>
     <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A45:A52"/>
-    <mergeCell ref="A29:A41"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="F13:F14"/>
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="A19:A28"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="F23:F24"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F27" r:id="rId1" location="2-hypothetical-baseline" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="F46" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F23" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F22" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="F13" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="F26" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="F33" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="F18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="F17" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="F20" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="F44" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="F6" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="F12" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="F7" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="F27" r:id="rId1" location="2-hypothetical-baseline" xr:uid="{90747F46-A1D4-4EAA-8AF1-CA9722839195}"/>
+    <hyperlink ref="F43" r:id="rId2" xr:uid="{DDDFF0F6-D15E-4E92-891D-7E7B8FAFF4F9}"/>
+    <hyperlink ref="F23" r:id="rId3" xr:uid="{87303D6C-B313-4D6B-AF5C-D27BE9BF7044}"/>
+    <hyperlink ref="F22" r:id="rId4" xr:uid="{6B9B5ACE-3380-4457-8BEC-B382A2EB51E5}"/>
+    <hyperlink ref="F13" r:id="rId5" xr:uid="{ECC1FA58-5E0A-4B30-BBB1-B980FC85A980}"/>
+    <hyperlink ref="F26" r:id="rId6" xr:uid="{7BDDD265-2093-4EDC-8804-7CB40CCCBEF8}"/>
+    <hyperlink ref="F33" r:id="rId7" xr:uid="{86815A44-317A-4A66-8B0C-1B56202CE055}"/>
+    <hyperlink ref="F18" r:id="rId8" xr:uid="{0C2D6E5B-9F29-4329-89E1-C5B4491FB37E}"/>
+    <hyperlink ref="F17" r:id="rId9" xr:uid="{A50107D7-409C-4C5D-80C1-575DF6891EBC}"/>
+    <hyperlink ref="F20" r:id="rId10" xr:uid="{059D5153-769E-4D6F-9E5C-663354D74B18}"/>
+    <hyperlink ref="F6" r:id="rId11" xr:uid="{F9CB642C-A4B1-4618-A465-D4004E3A9375}"/>
+    <hyperlink ref="F12" r:id="rId12" xr:uid="{42779A97-1814-42EF-959F-D0BBC3D5FA9A}"/>
+    <hyperlink ref="F7" r:id="rId13" xr:uid="{01BEA526-02BA-432C-A7D2-4969254F1013}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId15"/>
-  <ignoredErrors>
-    <ignoredError sqref="D43" formula="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -3489,54 +3252,54 @@
         <v>28</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D1" s="34" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="35" customFormat="1" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="213" t="s">
-        <v>61</v>
+      <c r="A2" s="204" t="s">
+        <v>57</v>
       </c>
       <c r="B2" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="166" t="s">
-        <v>98</v>
+      <c r="C2" s="157" t="s">
+        <v>90</v>
       </c>
       <c r="D2" s="31">
         <f>parameters!D7</f>
-        <v>1</v>
-      </c>
-      <c r="E2" s="167" t="s">
-        <v>64</v>
+        <v>20</v>
+      </c>
+      <c r="E2" s="158" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="35" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="213"/>
-      <c r="B3" s="85" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="164" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" s="85" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" s="165" t="s">
-        <v>124</v>
+      <c r="A3" s="204"/>
+      <c r="B3" s="80" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="155" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="80" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="156" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="208" t="s">
-        <v>72</v>
+      <c r="A4" s="190" t="s">
+        <v>66</v>
       </c>
       <c r="B4" s="44" t="str">
         <f>parameters!B8</f>
@@ -3553,7 +3316,7 @@
       <c r="E4" s="47"/>
     </row>
     <row r="5" spans="1:5" ht="46.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="209"/>
+      <c r="A5" s="191"/>
       <c r="B5" s="1" t="str">
         <f>parameters!B9</f>
         <v>PARAM0008</v>
@@ -3567,11 +3330,11 @@
         <v>All</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="209"/>
+      <c r="A6" s="191"/>
       <c r="B6" s="1" t="str">
         <f>parameters!B10</f>
         <v>PARAM0009</v>
@@ -3585,119 +3348,119 @@
         <v>NO</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="36.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="209"/>
+      <c r="A7" s="191"/>
       <c r="B7" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="210"/>
+      <c r="A8" s="192"/>
       <c r="B8" s="52" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="53" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D8" s="54" t="str">
-        <f>parameters!D11</f>
-        <v>/path/to/folder/MS1/IDSL.IPA</v>
+        <f>_xlfn.CONCAT(parameters!D11, "/targted_IPA")</f>
+        <v>/path/to/folder/MS1/IDSL.IPA/targted_IPA</v>
       </c>
       <c r="E8" s="55"/>
     </row>
     <row r="9" spans="1:5" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="215" t="s">
-        <v>85</v>
+      <c r="A9" s="206" t="s">
+        <v>78</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C9" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="207"/>
+      <c r="B10" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="69.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="126" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" s="51" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="204"/>
-      <c r="B10" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="69.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="131" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" s="65" t="str">
+      <c r="B11" s="61" t="str">
         <f>parameters!B14</f>
         <v>PARAM0012</v>
       </c>
-      <c r="C11" s="128" t="str">
+      <c r="C11" s="123" t="str">
         <f>parameters!C14</f>
         <v>Mass difference between ion-pairs. This module always pairs dominant ions with lower intensity ions in a fixed distance. To pair dominant ions with lower mass ions, negative values should be used for this parameter.</v>
       </c>
-      <c r="D11" s="67">
+      <c r="D11" s="63">
         <f>parameters!D14</f>
         <v>1.003354835336</v>
       </c>
-      <c r="E11" s="66" t="str">
+      <c r="E11" s="62" t="str">
         <f>parameters!E14</f>
         <v>(Default = ∆C = 13C - 12C = 1.003354835336 to only find carbon-containing peaks), ∆S = 34S - 32S = 1.9957958356, or any numerical value</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="198" t="s">
+      <c r="A12" s="197" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="63" t="str">
+      <c r="B12" s="59" t="str">
         <f>parameters!B15</f>
         <v>PARAM0013</v>
       </c>
-      <c r="C12" s="124" t="str">
+      <c r="C12" s="119" t="str">
         <f>parameters!C15</f>
         <v>Mass accuracy (Da) to cluster m/z values and generate extracted ion chromatograms (EICs)</v>
       </c>
-      <c r="D12" s="63">
+      <c r="D12" s="59">
         <f>parameters!D15</f>
         <v>0.01</v>
       </c>
-      <c r="E12" s="124" t="str">
+      <c r="E12" s="119" t="str">
         <f>parameters!E15</f>
         <v>≤ 0.01</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="199"/>
+      <c r="A13" s="198"/>
       <c r="B13" s="8" t="str">
         <f>parameters!B17</f>
         <v>PARAM0015</v>
       </c>
-      <c r="C13" s="125" t="str">
+      <c r="C13" s="120" t="str">
         <f>parameters!C17</f>
         <v>Smoothing window (number of MS1 scans)</v>
       </c>
@@ -3705,63 +3468,63 @@
         <f>parameters!D17</f>
         <v>12</v>
       </c>
-      <c r="E13" s="125" t="str">
+      <c r="E13" s="120" t="str">
         <f>parameters!E17</f>
         <v>≥ 5</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="216"/>
-      <c r="B14" s="74" t="str">
+      <c r="A14" s="208"/>
+      <c r="B14" s="70" t="str">
         <f>parameters!B18</f>
         <v>PARAM0017</v>
       </c>
-      <c r="C14" s="126" t="str">
+      <c r="C14" s="121" t="str">
         <f>parameters!C18</f>
         <v>Peak tailing/fronting resolving power</v>
       </c>
-      <c r="D14" s="74">
+      <c r="D14" s="70">
         <f>parameters!D18</f>
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="E14" s="126" t="str">
+      <c r="E14" s="121" t="str">
         <f>parameters!E18</f>
         <v>0-0.05 (Select 0 to skip this module)</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="41.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="214" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="70" t="str">
+      <c r="A15" s="205" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="66" t="str">
         <f>parameters!B20</f>
         <v>PARAM0020</v>
       </c>
-      <c r="C15" s="129" t="str">
+      <c r="C15" s="124" t="str">
         <f>parameters!C20</f>
         <v>Number of extra scans on the both sides of detected peak boundaries in the recursive analysis to reconstruct baseline</v>
       </c>
-      <c r="D15" s="70">
+      <c r="D15" s="66">
         <f>parameters!D20</f>
         <v>100</v>
       </c>
-      <c r="E15" s="71"/>
+      <c r="E15" s="67"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="202"/>
-      <c r="B16" s="77" t="str">
+      <c r="A16" s="201"/>
+      <c r="B16" s="73" t="str">
         <f>parameters!B28</f>
         <v>PARAM0028</v>
       </c>
-      <c r="C16" s="127" t="str">
+      <c r="C16" s="122" t="str">
         <f>parameters!C28</f>
         <v>Number of points to smooth individual chromatographic peaks using cubic spline method to calculate ancillary chromatography parameters</v>
       </c>
-      <c r="D16" s="77">
+      <c r="D16" s="73">
         <f>parameters!D28</f>
         <v>100</v>
       </c>
-      <c r="E16" s="127" t="str">
+      <c r="E16" s="122" t="str">
         <f>parameters!E28</f>
         <v>11-1000 (integer) (Select `0` to skip calculating ancillary chromatography parameters for faster computations)</v>
       </c>
